--- a/output/xgb_reg/04_model_report/XGBoost_回归评估_自定义分桶.xlsx
+++ b/output/xgb_reg/04_model_report/XGBoost_回归评估_自定义分桶.xlsx
@@ -490,16 +490,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.9755</v>
+        <v>2.9754</v>
       </c>
       <c r="C2" t="n">
-        <v>2.3675</v>
+        <v>2.3679</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0001</v>
+        <v>-0</v>
       </c>
       <c r="E2" t="n">
-        <v>128.6282</v>
+        <v>126.8424</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -519,13 +519,13 @@
         <v>2.9162</v>
       </c>
       <c r="C3" t="n">
-        <v>2.0777</v>
+        <v>2.0779</v>
       </c>
       <c r="D3" t="n">
         <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>102.0613</v>
+        <v>101.3268</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.9948</v>
+        <v>2.9962</v>
       </c>
       <c r="C4" t="n">
-        <v>2.3937</v>
+        <v>2.3949</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0184</v>
+        <v>-0.0193</v>
       </c>
       <c r="E4" t="n">
-        <v>136.0461</v>
+        <v>133.9121</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,17 +633,17 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>误差(预测-真实)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>MAE</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>MAPE(%)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>误差(预测-真实)</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[-7.8595, -2.97395]</t>
+          <t>[-inf, -3.0]</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -677,22 +677,22 @@
         <v>-4.4309</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="L2" t="n">
-        <v>4.2324</v>
+        <v>4.2425</v>
       </c>
       <c r="M2" t="n">
-        <v>95.23099999999999</v>
+        <v>4.2426</v>
       </c>
       <c r="N2" t="n">
-        <v>4.2323</v>
+        <v>95.4759</v>
       </c>
     </row>
     <row r="3">
@@ -706,7 +706,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(-2.97395, -1.50295]</t>
+          <t>(-3.0, -1.5]</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -725,22 +725,22 @@
         <v>-2.1316</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="L3" t="n">
-        <v>1.933</v>
+        <v>1.9432</v>
       </c>
       <c r="M3" t="n">
-        <v>90.3725</v>
+        <v>1.9432</v>
       </c>
       <c r="N3" t="n">
-        <v>1.933</v>
+        <v>90.8668</v>
       </c>
     </row>
     <row r="4">
@@ -754,7 +754,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>(-1.50295, -0.481]</t>
+          <t>(-1.5, -0.5]</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -773,22 +773,22 @@
         <v>-0.9413</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7428</v>
+        <v>0.7529</v>
       </c>
       <c r="M4" t="n">
-        <v>76.1168</v>
+        <v>0.753</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7427</v>
+        <v>77.343</v>
       </c>
     </row>
     <row r="5">
@@ -802,7 +802,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>(-0.481, 0.45845]</t>
+          <t>(-0.5, 0.5]</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -821,22 +821,22 @@
         <v>0.0487</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2972</v>
+        <v>-0.2371</v>
       </c>
       <c r="M5" t="n">
-        <v>366.7579</v>
+        <v>0.2898</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2473</v>
+        <v>350.2609</v>
       </c>
     </row>
     <row r="6">
@@ -850,7 +850,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>(0.45845, 1.5435]</t>
+          <t>(0.5, 1.5]</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -869,22 +869,22 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="L6" t="n">
-        <v>1.1517</v>
+        <v>-1.1415</v>
       </c>
       <c r="M6" t="n">
-        <v>123.6238</v>
+        <v>1.1415</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1517</v>
+        <v>122.4109</v>
       </c>
     </row>
     <row r="7">
@@ -898,7 +898,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>(1.5435, 3.09205]</t>
+          <t>(1.5, 3.0]</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -917,22 +917,22 @@
         <v>2.2973</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="L7" t="n">
-        <v>2.4958</v>
+        <v>-2.4857</v>
       </c>
       <c r="M7" t="n">
-        <v>109.089</v>
+        <v>2.4856</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.4959</v>
+        <v>108.6223</v>
       </c>
     </row>
     <row r="8">
@@ -946,7 +946,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>(3.09205, 7.5754]</t>
+          <t>(3.0, +inf]</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -965,70 +965,72 @@
         <v>4.7692</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="L8" t="n">
-        <v>4.9678</v>
+        <v>-4.9576</v>
       </c>
       <c r="M8" t="n">
-        <v>104.45</v>
+        <v>4.9576</v>
       </c>
       <c r="N8" t="n">
-        <v>-4.9678</v>
+        <v>104.2215</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>验证集</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+          <t>训练集</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>195</v>
+      </c>
+      <c r="E9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>[-8.1939, -3.01315]</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>7</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.1429</v>
-      </c>
       <c r="F9" t="n">
-        <v>-8.193899999999999</v>
+        <v>-7.8595</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.3508</v>
+        <v>7.5754</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.7481</v>
+        <v>-0.1689</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="L9" t="n">
-        <v>4.5496</v>
+        <v>-0.0195</v>
       </c>
       <c r="M9" t="n">
-        <v>95.4113</v>
+        <v>2.3679</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5495</v>
+        <v>126.8424</v>
       </c>
     </row>
     <row r="10">
@@ -1038,11 +1040,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>(-3.01315, -1.40715]</t>
+          <t>[-inf, -3.0]</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1052,31 +1054,31 @@
         <v>0.1429</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.6755</v>
+        <v>-8.193899999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5086</v>
+        <v>-3.3508</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9844</v>
+        <v>-4.7481</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="L10" t="n">
-        <v>1.7858</v>
+        <v>4.5597</v>
       </c>
       <c r="M10" t="n">
-        <v>89.6772</v>
+        <v>4.5598</v>
       </c>
       <c r="N10" t="n">
-        <v>1.7858</v>
+        <v>95.6469</v>
       </c>
     </row>
     <row r="11">
@@ -1086,11 +1088,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>(-1.40715, -0.55245]</t>
+          <t>(-3.0, -1.5]</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1100,31 +1102,31 @@
         <v>0.1429</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3057</v>
+        <v>-2.6755</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7016</v>
+        <v>-1.5086</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.0452</v>
+        <v>-1.9844</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8466</v>
+        <v>1.796</v>
       </c>
       <c r="M11" t="n">
-        <v>79.71980000000001</v>
+        <v>1.796</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8466</v>
+        <v>90.2072</v>
       </c>
     </row>
     <row r="12">
@@ -1134,45 +1136,45 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>(-0.55245, 0.4169]</t>
+          <t>(-1.5, -0.5]</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1837</v>
+        <v>0.1429</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4033</v>
+        <v>-1.3057</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2082</v>
+        <v>-0.7016</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1696</v>
+        <v>-1.0452</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="L12" t="n">
-        <v>0.145</v>
+        <v>0.8568</v>
       </c>
       <c r="M12" t="n">
-        <v>106.3727</v>
+        <v>0.8568</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.029</v>
+        <v>80.761</v>
       </c>
     </row>
     <row r="13">
@@ -1182,45 +1184,45 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>(0.4169, 1.30585]</t>
+          <t>(-0.5, 0.5]</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1633</v>
+        <v>0.1837</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6256</v>
+        <v>-0.4033</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9038</v>
+        <v>0.2082</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7647</v>
+        <v>-0.1696</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="L13" t="n">
-        <v>0.9633</v>
+        <v>-0.0188</v>
       </c>
       <c r="M13" t="n">
-        <v>126.5193</v>
+        <v>0.1439</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9633</v>
+        <v>102.6226</v>
       </c>
     </row>
     <row r="14">
@@ -1230,45 +1232,45 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>(1.30585, 2.83495]</t>
+          <t>(0.5, 1.5]</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1224</v>
+        <v>0.1633</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7079</v>
+        <v>0.6256</v>
       </c>
       <c r="G14" t="n">
-        <v>2.5928</v>
+        <v>0.9038</v>
       </c>
       <c r="H14" t="n">
-        <v>2.1296</v>
+        <v>0.7647</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="L14" t="n">
-        <v>2.3282</v>
+        <v>-0.9530999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>109.5443</v>
+        <v>0.9530999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.3282</v>
+        <v>125.1577</v>
       </c>
     </row>
     <row r="15">
@@ -1278,141 +1280,143 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>(2.83495, 8.5034]</t>
+          <t>(1.5, 3.0]</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>0.102</v>
+        <v>0.1224</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0771</v>
+        <v>1.7079</v>
       </c>
       <c r="G15" t="n">
-        <v>8.503399999999999</v>
+        <v>2.5928</v>
       </c>
       <c r="H15" t="n">
-        <v>5.5118</v>
+        <v>2.1296</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="L15" t="n">
-        <v>5.7104</v>
+        <v>-2.318</v>
       </c>
       <c r="M15" t="n">
-        <v>104.1144</v>
+        <v>2.318</v>
       </c>
       <c r="N15" t="n">
-        <v>-5.7104</v>
+        <v>109.0542</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OOT</t>
+          <t>验证集</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[-11.5448, -2.9924]</t>
+          <t>(3.0, +inf]</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>570</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2068</v>
+        <v>0.102</v>
       </c>
       <c r="F16" t="n">
-        <v>-11.5448</v>
+        <v>3.0771</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.004</v>
+        <v>8.503399999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>-4.6362</v>
+        <v>5.5118</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="L16" t="n">
-        <v>4.4376</v>
+        <v>-5.7002</v>
       </c>
       <c r="M16" t="n">
-        <v>95.3595</v>
+        <v>5.7002</v>
       </c>
       <c r="N16" t="n">
-        <v>4.4376</v>
+        <v>103.9031</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OOT</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2</v>
+          <t>验证集</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>(-2.9924, -1.50025]</t>
+          <t>All</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>494</v>
+        <v>49</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1792</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.9808</v>
+        <v>-8.193899999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.5009</v>
+        <v>8.503399999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.2527</v>
+        <v>-0.1942</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="L17" t="n">
-        <v>2.0542</v>
+        <v>0.0058</v>
       </c>
       <c r="M17" t="n">
-        <v>90.8421</v>
+        <v>2.0779</v>
       </c>
       <c r="N17" t="n">
-        <v>2.0541</v>
+        <v>101.3268</v>
       </c>
     </row>
     <row r="18">
@@ -1422,45 +1426,45 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>(-1.50025, -0.50165]</t>
+          <t>[-inf, -3.0]</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>370</v>
+        <v>570</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1343</v>
+        <v>0.2068</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4996</v>
+        <v>-11.5448</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5056</v>
+        <v>-3.004</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9941</v>
+        <v>-4.6362</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7956</v>
+        <v>4.4478</v>
       </c>
       <c r="M18" t="n">
-        <v>78.22629999999999</v>
+        <v>4.4478</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7955</v>
+        <v>95.5977</v>
       </c>
     </row>
     <row r="19">
@@ -1470,45 +1474,45 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>(-0.50165, 0.49945]</t>
+          <t>(-3.0, -1.5]</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>348</v>
+        <v>494</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1263</v>
+        <v>0.1792</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4977</v>
+        <v>-2.9808</v>
       </c>
       <c r="G19" t="n">
-        <v>0.496</v>
+        <v>-1.5009</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0075</v>
+        <v>-2.2527</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2755</v>
+        <v>2.0643</v>
       </c>
       <c r="M19" t="n">
-        <v>395.7568</v>
+        <v>2.0644</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1911</v>
+        <v>91.31229999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1518,45 +1522,45 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>(0.49945, 1.5003]</t>
+          <t>(-1.5, -0.5]</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>310</v>
+        <v>370</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1125</v>
+        <v>0.1343</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5029</v>
+        <v>-1.4996</v>
       </c>
       <c r="G20" t="n">
-        <v>1.499</v>
+        <v>-0.5056</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9922</v>
+        <v>-0.9941</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="L20" t="n">
-        <v>1.1907</v>
+        <v>0.8057</v>
       </c>
       <c r="M20" t="n">
-        <v>122.051</v>
+        <v>0.8058</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1908</v>
+        <v>79.3442</v>
       </c>
     </row>
     <row r="21">
@@ -1566,45 +1570,45 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>(1.5003, 3.0038]</t>
+          <t>(-0.5, 0.5]</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1274</v>
+        <v>0.1263</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5016</v>
+        <v>-0.4977</v>
       </c>
       <c r="G21" t="n">
-        <v>2.9966</v>
+        <v>0.496</v>
       </c>
       <c r="H21" t="n">
-        <v>2.1761</v>
+        <v>-0.0075</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="L21" t="n">
-        <v>2.3747</v>
+        <v>-0.1809</v>
       </c>
       <c r="M21" t="n">
-        <v>109.4813</v>
+        <v>0.2717</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.3747</v>
+        <v>378.3281</v>
       </c>
     </row>
     <row r="22">
@@ -1614,48 +1618,204 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>(0.5, 1.5]</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>310</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.1125</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.5029</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.499</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.9922</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.1884</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-0.1884</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-0.1884</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-1.1806</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.1805</v>
+      </c>
+      <c r="N22" t="n">
+        <v>120.9188</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>OOT</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>6</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>(1.5, 3.0]</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>351</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.1274</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.5016</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.9966</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.1761</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-0.1884</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-0.1884</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-0.1884</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-2.3645</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2.3645</v>
+      </c>
+      <c r="N23" t="n">
+        <v>108.9945</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>OOT</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
         <v>7</v>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>(3.0038, 11.4595]</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>(3.0, +inf]</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>313</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E24" t="n">
         <v>0.1136</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F24" t="n">
         <v>3.011</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G24" t="n">
         <v>11.4595</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H24" t="n">
         <v>4.4658</v>
       </c>
-      <c r="I22" t="n">
-        <v>-0.1986</v>
-      </c>
-      <c r="J22" t="n">
-        <v>-0.1986</v>
-      </c>
-      <c r="K22" t="n">
-        <v>-0.1986</v>
-      </c>
-      <c r="L22" t="n">
-        <v>4.6644</v>
-      </c>
-      <c r="M22" t="n">
-        <v>104.7326</v>
-      </c>
-      <c r="N22" t="n">
-        <v>-4.6644</v>
+      <c r="I24" t="n">
+        <v>-0.1884</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-0.1884</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.1884</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-4.6542</v>
+      </c>
+      <c r="M24" t="n">
+        <v>4.6542</v>
+      </c>
+      <c r="N24" t="n">
+        <v>104.4896</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>OOT</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2756</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-11.5448</v>
+      </c>
+      <c r="G25" t="n">
+        <v>11.4595</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.6011</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.1884</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.1884</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.1884</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.4127</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2.3949</v>
+      </c>
+      <c r="N25" t="n">
+        <v>133.9121</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="N2:N25">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF4472C4"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1666,7 +1826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1727,17 +1887,17 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>误差(预测-真实)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>MAE</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>MAPE(%)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>误差(预测-真实)</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1912,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[-0.1986, -0.1986]</t>
+          <t>(-0.5, 0.5]</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -1771,76 +1931,78 @@
         <v>-0.1689</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="L2" t="n">
-        <v>2.3675</v>
+        <v>-0.0195</v>
       </c>
       <c r="M2" t="n">
-        <v>128.6282</v>
+        <v>2.3679</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0297</v>
+        <v>126.8424</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>验证集</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>4</v>
+          <t>训练集</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[-0.1986, -0.1986]</t>
+          <t>All</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>49</v>
+        <v>195</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>-8.193899999999999</v>
+        <v>-7.8595</v>
       </c>
       <c r="G3" t="n">
-        <v>8.503399999999999</v>
+        <v>7.5754</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1942</v>
+        <v>-0.1689</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1986</v>
+        <v>-0.1884</v>
       </c>
       <c r="L3" t="n">
-        <v>2.0777</v>
+        <v>-0.0195</v>
       </c>
       <c r="M3" t="n">
-        <v>102.0613</v>
+        <v>2.3679</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0044</v>
+        <v>126.8424</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OOT</t>
+          <t>验证集</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1848,44 +2010,202 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[-0.1986, -0.1986]</t>
+          <t>(-0.5, 0.5]</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2756</v>
+        <v>49</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
+        <v>-8.193899999999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>8.503399999999999</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.1942</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0.1884</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-0.1884</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.1884</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.0779</v>
+      </c>
+      <c r="N4" t="n">
+        <v>101.3268</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>验证集</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>49</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-8.193899999999999</v>
+      </c>
+      <c r="G5" t="n">
+        <v>8.503399999999999</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.1942</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.1884</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-0.1884</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0.1884</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.0779</v>
+      </c>
+      <c r="N5" t="n">
+        <v>101.3268</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>OOT</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>(-0.5, 0.5]</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2756</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
         <v>-11.5448</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G6" t="n">
         <v>11.4595</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H6" t="n">
         <v>-0.6011</v>
       </c>
-      <c r="I4" t="n">
-        <v>-0.1986</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-0.1986</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-0.1986</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2.3937</v>
-      </c>
-      <c r="M4" t="n">
-        <v>136.0461</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.4025</v>
+      <c r="I6" t="n">
+        <v>-0.1884</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-0.1884</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0.1884</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.4127</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.3949</v>
+      </c>
+      <c r="N6" t="n">
+        <v>133.9121</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>OOT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2756</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-11.5448</v>
+      </c>
+      <c r="G7" t="n">
+        <v>11.4595</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.6011</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-0.1884</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-0.1884</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.1884</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.4127</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.3949</v>
+      </c>
+      <c r="N7" t="n">
+        <v>133.9121</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="N2:N7">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF4472C4"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1896,7 +2216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C90"/>
+  <dimension ref="A1:C91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1928,14 +2248,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[-3.03, -3.0]</t>
+          <t>[-inf, -3.0]</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>95.23</v>
+        <v>95.48</v>
       </c>
       <c r="C3" t="n">
-        <v>95.23</v>
+        <v>95.48</v>
       </c>
     </row>
     <row r="4">
@@ -1945,10 +2265,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>90.37</v>
+        <v>90.87</v>
       </c>
       <c r="C4" t="n">
-        <v>90.37</v>
+        <v>90.87</v>
       </c>
     </row>
     <row r="5">
@@ -1958,10 +2278,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>76.12</v>
+        <v>77.34</v>
       </c>
       <c r="C5" t="n">
-        <v>76.12</v>
+        <v>77.34</v>
       </c>
     </row>
     <row r="6">
@@ -1971,10 +2291,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>366.76</v>
+        <v>350.26</v>
       </c>
       <c r="C6" t="n">
-        <v>366.76</v>
+        <v>350.26</v>
       </c>
     </row>
     <row r="7">
@@ -1984,10 +2304,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>123.62</v>
+        <v>122.41</v>
       </c>
       <c r="C7" t="n">
-        <v>123.62</v>
+        <v>122.41</v>
       </c>
     </row>
     <row r="8">
@@ -1997,23 +2317,23 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>109.09</v>
+        <v>108.62</v>
       </c>
       <c r="C8" t="n">
-        <v>109.09</v>
+        <v>108.62</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>(3.0, 3.03]</t>
+          <t>(3.0, +inf]</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>104.45</v>
+        <v>104.22</v>
       </c>
       <c r="C9" t="n">
-        <v>104.45</v>
+        <v>104.22</v>
       </c>
     </row>
     <row r="10">
@@ -2023,10 +2343,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>128.63</v>
+        <v>126.84</v>
       </c>
       <c r="C10" t="n">
-        <v>128.63</v>
+        <v>126.84</v>
       </c>
     </row>
     <row r="11">
@@ -2046,7 +2366,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[-3.03, -3.0]</t>
+          <t>[-inf, -3.0]</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2124,7 +2444,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>(3.0, 3.03]</t>
+          <t>(3.0, +inf]</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2164,7 +2484,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>[-3.03, -3.0]</t>
+          <t>[-inf, -3.0]</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2242,7 +2562,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>(3.0, 3.03]</t>
+          <t>(3.0, +inf]</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2282,14 +2602,14 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>[-3.03, -3.0]</t>
+          <t>[-inf, -3.0]</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>95.41</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>95.41</v>
+        <v>95.65000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -2299,10 +2619,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>89.68000000000001</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>89.68000000000001</v>
+        <v>90.20999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -2312,10 +2632,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>79.72</v>
+        <v>80.76000000000001</v>
       </c>
       <c r="C35" t="n">
-        <v>79.72</v>
+        <v>80.76000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -2325,10 +2645,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>106.37</v>
+        <v>102.62</v>
       </c>
       <c r="C36" t="n">
-        <v>106.37</v>
+        <v>102.62</v>
       </c>
     </row>
     <row r="37">
@@ -2338,10 +2658,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>126.52</v>
+        <v>125.16</v>
       </c>
       <c r="C37" t="n">
-        <v>126.52</v>
+        <v>125.16</v>
       </c>
     </row>
     <row r="38">
@@ -2351,23 +2671,23 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>109.54</v>
+        <v>109.05</v>
       </c>
       <c r="C38" t="n">
-        <v>109.54</v>
+        <v>109.05</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>(3.0, 3.03]</t>
+          <t>(3.0, +inf]</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>104.11</v>
+        <v>103.9</v>
       </c>
       <c r="C39" t="n">
-        <v>104.11</v>
+        <v>103.9</v>
       </c>
     </row>
     <row r="40">
@@ -2377,10 +2697,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>102.06</v>
+        <v>101.33</v>
       </c>
       <c r="C40" t="n">
-        <v>102.06</v>
+        <v>101.33</v>
       </c>
     </row>
     <row r="41">
@@ -2400,7 +2720,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>[-3.03, -3.0]</t>
+          <t>[-inf, -3.0]</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2478,7 +2798,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>(3.0, 3.03]</t>
+          <t>(3.0, +inf]</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2518,7 +2838,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>[-3.03, -3.0]</t>
+          <t>[-inf, -3.0]</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2596,7 +2916,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>(3.0, 3.03]</t>
+          <t>(3.0, +inf]</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -2636,14 +2956,14 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>[-3.03, -3.0]</t>
+          <t>[-inf, -3.0]</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>95.36</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="C63" t="n">
-        <v>95.36</v>
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -2653,10 +2973,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>90.84</v>
+        <v>91.31</v>
       </c>
       <c r="C64" t="n">
-        <v>90.84</v>
+        <v>91.31</v>
       </c>
     </row>
     <row r="65">
@@ -2666,10 +2986,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>78.23</v>
+        <v>79.34</v>
       </c>
       <c r="C65" t="n">
-        <v>78.23</v>
+        <v>79.34</v>
       </c>
     </row>
     <row r="66">
@@ -2679,10 +2999,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>395.76</v>
+        <v>378.33</v>
       </c>
       <c r="C66" t="n">
-        <v>395.76</v>
+        <v>378.33</v>
       </c>
     </row>
     <row r="67">
@@ -2692,10 +3012,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>122.05</v>
+        <v>120.92</v>
       </c>
       <c r="C67" t="n">
-        <v>122.05</v>
+        <v>120.92</v>
       </c>
     </row>
     <row r="68">
@@ -2705,23 +3025,23 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>109.48</v>
+        <v>108.99</v>
       </c>
       <c r="C68" t="n">
-        <v>109.48</v>
+        <v>108.99</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>(3.0, 3.03]</t>
+          <t>(3.0, +inf]</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>104.73</v>
+        <v>104.49</v>
       </c>
       <c r="C69" t="n">
-        <v>104.73</v>
+        <v>104.49</v>
       </c>
     </row>
     <row r="70">
@@ -2731,10 +3051,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>136.05</v>
+        <v>133.91</v>
       </c>
       <c r="C70" t="n">
-        <v>136.05</v>
+        <v>133.91</v>
       </c>
     </row>
     <row r="71">
@@ -2754,7 +3074,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>[-3.03, -3.0]</t>
+          <t>[-inf, -3.0]</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -2832,7 +3152,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>(3.0, 3.03]</t>
+          <t>(3.0, +inf]</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -2872,7 +3192,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>[-3.03, -3.0]</t>
+          <t>[-inf, -3.0]</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -2950,7 +3270,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>(3.0, 3.03]</t>
+          <t>(3.0, +inf]</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -2973,7 +3293,95 @@
         <v>1</v>
       </c>
     </row>
+    <row r="91"/>
   </sheetData>
+  <conditionalFormatting sqref="B3:B9">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="max"/>
+        <color rgb="00FF0000"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13:B19">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF4472C4"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B23:B29">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF4472C4"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B33:B39">
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="max"/>
+        <color rgb="00FF0000"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B43:B49">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF4472C4"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B53:B59">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF4472C4"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B63:B69">
+    <cfRule type="dataBar" priority="7">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="max"/>
+        <color rgb="00FF0000"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B73:B79">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF4472C4"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B83:B89">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF4472C4"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>